--- a/main/StructureDefinition-bc-operation-outcome.xlsx
+++ b/main/StructureDefinition-bc-operation-outcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T21:39:06+00:00</t>
+    <t>2026-04-01T23:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -355,7 +355,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -597,7 +597,7 @@
     <t>A code that provides details as the exact issue.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/operation-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/operation-outcome|4.0.1</t>
   </si>
   <si>
     <t>ERR-5</t>
@@ -1181,7 +1181,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="38.43359375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="37.93359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.02734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2931,7 +2931,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>179</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>193</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>204</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>219</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>241</v>
       </c>
@@ -4561,12 +4561,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL31">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
